--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Azure ML</t>
+          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb0603438f1b772</t>
+          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, GitHub Actions, Git, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Tableau</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PyTorch, OpenCV, Docker, Kubernetes, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Auctane</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Terraform, Git, NoSQL, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e1325d0f888cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Data Lake, Docker, CI/CD, Databricks</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1de6d8eaa0bd49d</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Hadoop, R, Java</t>
+          <t>Generative AI, RAG, Cortex, Apache Airflow, Terraform, Git, Snowflake, Tableau, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Integration Engineer</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Glue, Terraform, Git, Kafka, Python, R</t>
+          <t>AI Engineer, RAG, AWS SageMaker, MLflow, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876d2ec7a7f5d033</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - SAP Test Automation</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6321bb282d47c1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=36f238a88a037bfb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QA Engineer - Gen AI</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sustainment</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, MLflow, Kubernetes, CI/CD, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+          <t>https://www.indeed.com/viewjob?jk=94ca6d649fa4d8eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stash</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, AKS, CI/CD, GitHub Actions, Git, Redshift, Python, SQL</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac34b813e80e169</t>
+          <t>https://www.indeed.com/viewjob?jk=db6098926b44304f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - SAP Test Automation</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40810b7e2f2c189e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4742366682aa86</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b14cd6d488a5abb</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fbf1adaeaec048</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70913b37ac8595e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technology Risk Specialist | Technology Risk Management</t>
+          <t>Solution Builder</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Python, SQL, R, Scala</t>
+          <t>LangChain, LLaMA, Prompt Engineering, BigQuery, AKS, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=335e30ad9a7743e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7a23bc5885b9fc99</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kafka, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior SDET, PAM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>ACCO Engineered Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, Apache Airflow, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42063640637c9d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Software Engineer, Machine Learning (SWE II &amp; SWE I)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, AKS, CI/CD, PySpark, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Keras, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcd5fe227c001c4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Databricks, PySpark, Hadoop, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer III - API Hub - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Owl Labs</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7383687e3e9016</t>
+          <t>https://www.indeed.com/viewjob?jk=761897fa19b321ae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Owl Labs</t>
+          <t>Enverus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Kafka, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,1582 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71d06adc0eea81c</t>
+          <t>https://www.indeed.com/viewjob?jk=bed46b825142013f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Owl Labs</t>
+          <t>Enverus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Kafka, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f239d30c2ac7fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Enverus</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Kafka, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=419c955d26d0b56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Enverus</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Spokane, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Kafka, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5785e91e635c4748</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer (Rapid Application Development) - New York</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dechert LLP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be49847cba938f3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer (Rapid Application Development) - Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dechert LLP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=042757f2a2c78294</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (Customer Engineering, Prisma AIRS)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8954ae6b8014fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IT Sr. Analyst, AI Engineer (Elkhart, Indiana, US, 46516)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Patrick Industries</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Elkhart, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37288b4967880fd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Acima Leasing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, Git, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c96a69688cc4abaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Acima Leasing</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, Git, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d3e74478ecb4318</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Hadoop, PostgreSQL, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0db6135802ab6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SecDevOps Engineer (Jr.)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knox Systems</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8204887a7f10d775</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SecDevOps Engineer (Jr.)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knox Systems</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd9bf015156448a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Database Engineer I,II,III, SR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tinker Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Synapse, Dataflow, CI/CD, Snowflake, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Platform Engineer IV</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60e242f35e0225aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OverHaul Group</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71f2221adde60f89</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a07f3a28e4d23eea</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>IT Analyst, AI Engineer (Elkhart, Indiana, US, 46516)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Patrick Industries</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Elkhart, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0230aad2426cbb0e</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e061857b52c878</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Research Engineer, Code Agents Infra</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Mistral, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bf0118998adedd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ce9aae77c474bd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c34ddd96325c0a41</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8e7eb8d4507240</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65465166bb20685d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3364449b61f6622</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa41990ad3c7ffc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b46e50ef755e5d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14b5e1be5e0537da</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbf8eb41d02fdc50</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ee2adde2625348d</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2bb255be8ce2441</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d3688bca4af825e</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e5746220dcd169d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=382f8c9a986bbd37</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=277f8718ddfd4ad8</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2087111e53b0ea9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1608468180e6b3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a726e6ab8300839f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5996c6186d9c5a69</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7c67d850b45cdb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb4fd4e3bedc1ff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior, Full Stack Engineer - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df3e36928e2617a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Applied AI</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Python, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcebf7d036818ff0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Fulton Bank</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Lancaster, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b64228b03cbd3509</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2027 Data for Good Hackathon - Data &amp; AI Program - Summer Internship</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=307ff3cbbf74ee48</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Solution Architect - Syndigo MDM- GCP</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da7e664002e4b2a8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Consultant – Modern Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Hadoop, MongoDB, Python</t>
+          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Apache Airflow, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6194bf1cf11624a3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Medlytix</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Python</t>
+          <t>LangChain, RAG, Copilot, S3, Data Lake, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>thelab</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a74b0b960aa360</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3838d41778bdd03a</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Direct Sales Analyst/Developer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,577 +626,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Data Lake, Docker, Kubernetes, Kafka, Python, R, Java</t>
+          <t>Generative AI, Redshift, Snowflake, Databricks, Redshift, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da4a43bb5f2b1660</t>
+          <t>https://www.indeed.com/viewjob?jk=8250748606454849</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>E2E Data and Analytics Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - HYBRID</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - HYBRID</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - HYBRID</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Java)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr. Engineer-Product Insights</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Snowflake, NoSQL, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50d65e53f6a4b1c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Automation Engineer 3 (Playwright, TypeScript &amp; JavaScript)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca15098b6b0ce046</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Automation Engineer 3 (Playwright, TypeScript &amp; JavaScript)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9123ece735a0db5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Automation Engineer 3 (Playwright, TypeScript &amp; JavaScript)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a4b6a81f0c6400</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Digible, Inc</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffeac6001256624f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Python Backend Software Engineer III- ML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc5fab86cea98ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sr Backend &amp; Data Engineer (Ad Factory)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ＡＮＧＥＬ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, Terraform, Snowflake, PostgreSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db69659ede67ce51</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Solution Architect - Syndigo MDM- GCP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6963827fdf562bee</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Cloud and DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Fieldpiece Instruments</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Kamas, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be3a9c413abbdf95</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Cloud and DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fieldpiece Instruments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b7cedcf250bb08</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>VFX AI Pipeline</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>thelab</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44f51e7d610554a8</t>
+          <t>https://www.indeed.com/viewjob?jk=88b462551d24506c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Consultant – Modern Data &amp; Analytics Engineering</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Apache Airflow, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6194bf1cf11624a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medlytix</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, S3, Data Lake, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Cassandra, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,94 +531,94 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
+          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Sec Ops Architect I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git</t>
+          <t>LangChain, RAG, Prompt Engineering, PyTorch, XGBoost, MLflow, Kubernetes, CI/CD, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=f236fd1058d34cfc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>A2Z Sync</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git</t>
+          <t>Prompt Engineering, S3, Glue, Athena, Data Lake, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Direct Sales Analyst/Developer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,297 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Redshift, Snowflake, Databricks, Redshift, Tableau, Python, SQL, R, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250748606454849</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E2E Data and Analytics Specialist</t>
+          <t>Medical Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hill's Pet Nutrition</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a37dd11f15a84b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Junior Full Stack Engineer (Java + React)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HK TECH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sandy, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cff6df5d9bbc0d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Eko Green Industrial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Miami Lakes, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Product Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Snowflake, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84196d7c9a7e2879</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Trainer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ced3750db486c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Escalon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88b462551d24506c</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a41cf2380f81449d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lennox International</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ac84de69c5084d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53814fa3decb268a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>31.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Cassandra, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
+          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sec Ops Architect I</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, PyTorch, XGBoost, MLflow, Kubernetes, CI/CD, Kafka, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Dataflow, Docker, Kubernetes, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f236fd1058d34cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A2Z Sync</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prompt Engineering, S3, Glue, Athena, Data Lake, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Medical Analytics Data Engineer</t>
+          <t>Senior Machine Learning (ML) Engineer (AI Insurtech)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>EvolutionIQ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, BigQuery, Kubernetes, Terraform, BigQuery, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a37dd11f15a84b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ac4aeac9693df4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Full Stack Engineer (Java + React)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HK TECH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cff6df5d9bbc0d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5342b691065f44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Product Deployed Engineer</t>
+          <t>Managing Solution Architect - Commercial Pharma &amp; Drug Manufacturers</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Snowflake, Databricks, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84196d7c9a7e2879</t>
+          <t>https://www.indeed.com/viewjob?jk=ae56665cdc5048af</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Trainer</t>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ced3750db486c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1dff99637a160c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,77 +846,742 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cf2380f81449d</t>
+          <t>https://www.indeed.com/viewjob?jk=05e0566691ed4fef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac84de69c5084d5</t>
+          <t>https://www.indeed.com/viewjob?jk=626667224500b860</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer</t>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6ad117672f6921b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bb1000dd9e992de</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fff50997c705fe99</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ba282c399ba9b18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=674d4be59200a109</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AmeriLife</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=746031e4f3020b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Associate Data and Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Blacksburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, MicroStrategy, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AmeriLife</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning Infrastructure Engineer, Technology</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Point72</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0c71dee7aff1a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81258ac487a1d651</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Java Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Jenkins, Terraform, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e37841033bdd6ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Associate Data and Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Blacksburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, MicroStrategy, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Solution Architect/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AAR Corp.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wood Dale, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend IoT &amp; Video Platform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SmartThings</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kinesis, Kubernetes, Terraform, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b04b66fad99ef2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Benjamin Moore</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Montvale, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04447ab048a23d1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e91c9bd81cc874b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer 4A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53814fa3decb268a</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8713d56bb71ded51</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Databricks Genie &amp; AI Analytics</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dev Technology Group</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fdd69d86b1290d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TopStep</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b7da76314b02749</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.1</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Git, Snowflake, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Dataflow, Docker, Kubernetes, Git, BigQuery, Kafka</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
+          <t>https://www.indeed.com/viewjob?jk=77ebf4f7fc4fa19b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=2596c97551c73aad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=84505f68573a4a62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning (ML) Engineer (AI Insurtech)</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EvolutionIQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, BigQuery, Kubernetes, Terraform, BigQuery, Python</t>
+          <t>FastAPI, Docker, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ac4aeac9693df4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5342b691065f44</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer II, Backend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Managing Solution Architect - Commercial Pharma &amp; Drug Manufacturers</t>
+          <t>Automation Engineer, Officer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae56665cdc5048af</t>
+          <t>https://www.indeed.com/viewjob?jk=b734b380ba99b4c2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>Automation Engineer, Officer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1dff99637a160c</t>
+          <t>https://www.indeed.com/viewjob?jk=83d89b3441f46848</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Generative AI, RAG, Glue, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e0566691ed4fef</t>
+          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Synapse Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Synapse, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626667224500b860</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b59b173e3606a2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>LLM Research Engineer IV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NuByt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Generative AI, LLaMA, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ad117672f6921b</t>
+          <t>https://www.indeed.com/viewjob?jk=17eebe5f2b26b7f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>LLM Research Engineer IV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NuByt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Generative AI, LLaMA, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb1000dd9e992de</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd0bec3fbdb18f4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff50997c705fe99</t>
+          <t>https://www.indeed.com/viewjob?jk=10a033881f24d2d0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba282c399ba9b18</t>
+          <t>https://www.indeed.com/viewjob?jk=1add8302a7ca053e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Java, Nest, React)</t>
+          <t>Software Developer, Advanced</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674d4be59200a109</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d799a5191c38a9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Developer, Advanced</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>West Mifflin, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4945b7ab4b9e1c59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
+          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746031e4f3020b93</t>
+          <t>https://www.indeed.com/viewjob?jk=53ec05ab624566d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior UI Developer- Angular v10+</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9429e33e512b7209</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence / Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>DESE Research, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=909a57dbc4b86f61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Infrastructure Engineer, Technology</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Wespath Benefits and Investments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glenview, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, Pinecone, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0c71dee7aff1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3aa5657e3e1a27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Tax, Salt Lake City, Associate, Software Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81258ac487a1d651</t>
+          <t>https://www.indeed.com/viewjob?jk=469a2e41302d8c3e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Java Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, Terraform, Git, SQL, R, Java</t>
+          <t>RAG, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e37841033bdd6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Mediacom Communications Corporation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Blooming Grove, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=bc35b8d1e1874634</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Hadoop, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,217 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Backend IoT &amp; Video Platform</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SmartThings</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Kinesis, Kubernetes, Terraform, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04b66fad99ef2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Benjamin Moore</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Montvale, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04447ab048a23d1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e91c9bd81cc874b</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Engineer 4A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8713d56bb71ded51</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Databricks Genie &amp; AI Analytics</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Dev Technology Group</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Databricks, PySpark, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdd69d86b1290d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>TopStep</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7da76314b02749</t>
+          <t>https://www.indeed.com/viewjob?jk=c0456ce4563b14ed</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Generative AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=48ef584643aa7bd1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Git, Snowflake, Databricks, Tableau, Power BI</t>
+          <t>Data Scientist, RAG, Glue, Data Lake, CI/CD, Terraform, Git, Snowflake, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ebf4f7fc4fa19b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd13dbcc3379f295</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2596c97551c73aad</t>
+          <t>https://www.indeed.com/viewjob?jk=641bed250d258ffa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84505f68573a4a62</t>
+          <t>https://www.indeed.com/viewjob?jk=89d6373e243bb52d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II, Backend</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Automation Engineer, Officer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b734b380ba99b4c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automation Engineer, Officer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d89b3441f46848</t>
+          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Glue, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
+          <t>FastAPI, Docker, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b59b173e3606a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLM Research Engineer IV</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NuByt</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, R, Scala</t>
+          <t>RAG, S3, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17eebe5f2b26b7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLM Research Engineer IV</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NuByt</t>
+          <t>GXO Logistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd0bec3fbdb18f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d703d29fbc667fff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, Python, SQL, R, Optimization</t>
+          <t>Cortex, S3, Apache Airflow, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a033881f24d2d0</t>
+          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1add8302a7ca053e</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Developer, Advanced</t>
+          <t>Senior Data Engineer - Forward Deployed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>Dataro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, S3, EC2, Athena, CI/CD, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d799a5191c38a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cda442182c42b1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer, Advanced</t>
+          <t>Software Engineer, Fleet Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>West Mifflin, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4945b7ab4b9e1c59</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9b97d67c10df93</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Git, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ec05ab624566d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3978f68291fa39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior UI Developer- Angular v10+</t>
+          <t>Software Support Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Git, PostgreSQL, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9429e33e512b7209</t>
+          <t>https://www.indeed.com/viewjob?jk=925cf5181974bda4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Artificial Intelligence / Machine Learning Engineer</t>
+          <t>Associate Full-stack Software Engineer (Intern)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DESE Research, Inc.</t>
+          <t>TrustScale</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+          <t>Generative AI, FastAPI, Docker, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909a57dbc4b86f61</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7f9e9a2b72c58a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Machine Learning Engineer, ML Infrastructure- Online</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wespath Benefits and Investments</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glenview, IL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Pinecone, Git, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3aa5657e3e1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=578b9e612e88a1de</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tax, Salt Lake City, Associate, Software Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469a2e41302d8c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7eb995e0ca5f36</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=3375e569456fd56f</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mediacom Communications Corporation</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Blooming Grove, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc35b8d1e1874634</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d471d15794b6a8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Machine Learning &amp; Computer Vision Scientist – R&amp;D (Junior/Associate)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>Elanco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Hadoop, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0456ce4563b14ed</t>
+          <t>https://www.indeed.com/viewjob?jk=50303eaee17e3047</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-05.xlsx
+++ b/daily_matches/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generative AI &amp; Machine Learning Engineer</t>
+          <t>Gen AI Solutions Engineer #122</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ef584643aa7bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Data Lake, CI/CD, Terraform, Git, Snowflake, Kafka, Power BI</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
+          <t>https://www.indeed.com/viewjob?jk=8d035334008dd47a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Expedient</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd13dbcc3379f295</t>
+          <t>https://www.indeed.com/viewjob?jk=0504ec969938a5ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641bed250d258ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d6373e243bb52d</t>
+          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Investment AI Solutions Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd9b315eefb8896</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, Hadoop, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=e283799e17891679</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>AI Agent Systems Architect - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Azumo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Pinecone, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=52d1b036a2b4a388</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>LLM Research Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Python, SQL</t>
+          <t>Generative AI, LLaMA, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bdfdc16a2520a6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Managing Solution Architect - Commercial Pharma &amp; Drug Manufacturers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=009e4b3acb23057b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Java</t>
+          <t>Gemini, BigQuery, CI/CD, Git, BigQuery, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Software/Platform Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2243095bf0eae58a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior .NET Engineer (Azure/ Kubernetes)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GXO Logistics</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, AKS, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d703d29fbc667fff</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1872e31acd3a34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer, Advanced</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cortex, S3, Apache Airflow, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc2a0065f7d7f74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer, Advanced</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Mifflin, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java, Scala</t>
+          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ca19932b81606b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Forward Deployed</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dataro</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Athena, CI/CD, Git, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, BigQuery, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cda442182c42b1</t>
+          <t>https://www.indeed.com/viewjob?jk=70d03a2c730a0fff</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, Fleet Platform</t>
+          <t>Senior Cloud/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9b97d67c10df93</t>
+          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Platform Engineer (Forward Deployment)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Git, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>AI Engineer, RAG, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3978f68291fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=30d390e6a6db8e93</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Support Engineer</t>
+          <t>Platform Engineer (Forward Deployment)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Git, PostgreSQL, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925cf5181974bda4</t>
+          <t>https://www.indeed.com/viewjob?jk=71fe7223b8ad43dd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Full-stack Software Engineer (Intern)</t>
+          <t>Platform Engineer (Forward Deployment)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TrustScale</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, FastAPI, Docker, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7f9e9a2b72c58a</t>
+          <t>https://www.indeed.com/viewjob?jk=82c2784ab1c1a7b8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, ML Infrastructure- Online</t>
+          <t>Applied Scientist, AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Red Violet, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578b9e612e88a1de</t>
+          <t>https://www.indeed.com/viewjob?jk=ba75f0edb04ddb2b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>ITgen systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Andes, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
+          <t>Generative AI, CI/CD, Terraform, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,112 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7eb995e0ca5f36</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Tachyon Technologies</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3375e569456fd56f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tachyon Technologies</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d471d15794b6a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Computer Vision Scientist – R&amp;D (Junior/Associate)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Elanco</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50303eaee17e3047</t>
+          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
         </is>
       </c>
     </row>
